--- a/docs/pin_list.xlsx
+++ b/docs/pin_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2da16fa1785921/MyDocuments/Community/ISHIKAI/shuttle/OpenSUSI-TR10/2026/ichiken_1bitCPU/OpenSUSI-TR1um-v2609_02/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2da16fa1785921/MyDocuments/Community/ISHIKAI/shuttle/OpenSUSI-TR10/2026/KOSEN/Gunma/OpenSUSI-TR1um-v2609/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="11_AD4D066CA252ABDACC1048686197E6B673EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633BB152-74F2-488B-A68D-929BC152D3ED}"/>
+  <xr:revisionPtr revIDLastSave="375" documentId="11_AD4D066CA252ABDACC1048686197E6B673EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2900AB0-A05A-4C23-ACA0-B3019CA45666}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38330" yWindow="0" windowWidth="19200" windowHeight="9980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
   <si>
     <t>Pin Number</t>
     <phoneticPr fontId="1"/>
@@ -44,38 +44,6 @@
   </si>
   <si>
     <t>VSS</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1bitCPU</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CLK</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>RESET</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>REG0</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PC0</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PC1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PROG1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PROG0</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -86,38 +54,23 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>OPAF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vinn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vinp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VOUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>none</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>inverter・共通</t>
-    <rPh sb="9" eb="11">
-      <t>キョウツウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>VDD</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>IN</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OUT</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>inverter・shkoga</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>inverter・TadasukeKuramochi</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>inverter・Luft256</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -542,10 +495,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -553,7 +506,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>8</v>
@@ -564,29 +517,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -595,29 +544,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3" ht="18.350000000000001" thickTop="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>4</v>
@@ -628,40 +573,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3" ht="18.350000000000001" thickTop="1">
       <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>18</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C13" s="2"/>
     </row>
@@ -670,21 +609,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18.350000000000001" thickTop="1">
@@ -692,18 +629,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>2</v>
